--- a/data/valuebets_database_2025-08-23.xlsx
+++ b/data/valuebets_database_2025-08-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>25/08 15:00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>110</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45892.0698690477</v>
+        <v>45892.06986905092</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>24/08 21:30</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>55</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45892.0698690477</v>
+        <v>45892.06986905092</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>26/08 00:10</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>70.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>70</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45892.0698690477</v>
+        <v>45892.06986905092</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>30/08 23:00</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>60</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45892.0698690477</v>
+        <v>45892.06986905092</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>24/08 18:30</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>60</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45892.0698690477</v>
+        <v>45892.06986905092</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>24/08 19:00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>55</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45892.0698690477</v>
+        <v>45892.06986905092</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>23/08 19:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>45</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45892.0698690477</v>
+        <v>45892.06986905092</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>24/08 15:30</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>60</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45892.0698690477</v>
+        <v>45892.06986905092</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>23/08 11:35</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>55</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45892.0698690477</v>
+        <v>45892.06986905092</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>25/08 20:00</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>55</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45892.0698690477</v>
+        <v>45892.06986905092</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>25/08 15:00</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>65.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>65</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45892.0698690477</v>
+        <v>45892.06986905092</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>25/08 22:00</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>55</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45892.0698690477</v>
+        <v>45892.06986905092</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>24/08 23:00</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>55</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45892.0698690477</v>
+        <v>45892.06986905092</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>24/08 14:30</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>55</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45892.0698690477</v>
+        <v>45892.06986905092</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>23/08 19:00</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F16" t="n">
+        <v>2.7</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45892.0698690477</v>
+        <v>45892.06986905092</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>31/08 14:45</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>55</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45892.0698690477</v>
+        <v>45892.06986905092</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>23/08 14:00</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>50</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45892.0698690477</v>
+        <v>45892.06986905092</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>31/08 00:00</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>60</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45892.0698690477</v>
+        <v>45892.06986905092</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>24/08 17:00</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>50</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45892.0698690477</v>
+        <v>45892.06986905092</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>25/08 01:30</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>50</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45892.0698690477</v>
+        <v>45892.06986905092</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>31/08 01:00</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>50</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45892.0698690477</v>
+        <v>45892.06986905092</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>24/08 19:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>55</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45892.0698690477</v>
+        <v>45892.06986905092</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>23/08 17:00</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>50</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45892.0698690477</v>
+        <v>45892.06986905092</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>23/08 10:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>50</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45892.0698690477</v>
+        <v>45892.06986905092</v>
       </c>
     </row>
     <row r="26">
@@ -1585,10 +1537,8 @@
           <t>24/08 12:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F26" t="n">
+        <v>60</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1601,7 +1551,142 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45892.0698690477</v>
+        <v>45892.06986905092</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 11.5 - tirs2e équipe | Trabzonspo</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Trabzonspor – AntalyasporTurquie - Turquie Super Lig</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Plus que 11.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>24/08 16:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>39,8%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+31,4%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45892.12788612599</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 9.5 - tir cadré | Columbus C</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Columbus Crew – New England RevolutionÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Moins que 9.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>23/08 23:30</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>54,9%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+12,6%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45892.12788612599</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | H 2 (−2.5) | Alexei Pop</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Alexei Popyrin – Emil RuusuvuoriUS Open (H)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>H 2 (−2.5)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>25/08 15:00</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+11,4%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45892.12788612599</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-23.xlsx
+++ b/data/valuebets_database_2025-08-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>24/08 16:00</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="F27" t="n">
+        <v>3.3</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45892.12788612599</v>
+        <v>45892.12788612268</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>23/08 23:30</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
+      <c r="F28" t="n">
+        <v>2.05</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45892.12788612599</v>
+        <v>45892.12788612268</v>
       </c>
     </row>
     <row r="29">
@@ -1670,10 +1666,8 @@
           <t>25/08 15:00</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>55</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1686,7 +1680,52 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45892.12788612599</v>
+        <v>45892.12788612268</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Gaziantep </t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Gaziantep FK – GenclerbirligiSüper Lig</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>23/08 18:30</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+11,3%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45892.18421069175</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-23.xlsx
+++ b/data/valuebets_database_2025-08-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1709,23 +1709,66 @@
           <t>23/08 18:30</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" t="n">
+        <v>50</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+11,3%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45892.18421069445</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Millonario</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Millonarios FC – Atletico JuniorPrimera A</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>24/08 01:30</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>50.00</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>+11,3%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>45892.18421069175</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+13,1%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45892.22209674055</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-23.xlsx
+++ b/data/valuebets_database_2025-08-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,10 +1752,8 @@
           <t>24/08 01:30</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>50</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1768,7 +1766,52 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45892.22209674055</v>
+        <v>45892.22209673611</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 2.5 - tir cadré2e équipe | Heidenheim</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Heidenheim – WolfsburgAllemagne - Allemagne Bundesliga</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Moins que 2.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>23/08 13:30</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>23,4%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+11,1%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45892.27073708516</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-23.xlsx
+++ b/data/valuebets_database_2025-08-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1795,10 +1795,8 @@
           <t>23/08 13:30</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
+      <c r="F32" t="n">
+        <v>4.75</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1811,7 +1809,142 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45892.27073708516</v>
+        <v>45892.27073708333</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 23.5 - tirs | Atletico M</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Atletico Madrid – ElcheLaLiga</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Moins que 23.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>23/08 17:30</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>40,7%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+26,1%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45892.3049916775</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | PSV Eindho</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven – GroningenEredivisie</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>23/08 16:45</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+20,8%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45892.3049916775</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Palerme – </t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Palerme – ReggianaSerie B</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>23/08 19:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+16,3%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45892.3049916775</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-23.xlsx
+++ b/data/valuebets_database_2025-08-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1838,10 +1838,8 @@
           <t>23/08 17:30</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="F33" t="n">
+        <v>3.1</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1854,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45892.3049916775</v>
+        <v>45892.30499167824</v>
       </c>
     </row>
     <row r="34">
@@ -1883,10 +1881,8 @@
           <t>23/08 16:45</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F34" t="n">
+        <v>60</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1899,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45892.3049916775</v>
+        <v>45892.30499167824</v>
       </c>
     </row>
     <row r="35">
@@ -1928,10 +1924,8 @@
           <t>23/08 19:00</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F35" t="n">
+        <v>50</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1944,7 +1938,142 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45892.3049916775</v>
+        <v>45892.30499167824</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Fenerbahce</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Fenerbahce – KocaelisporSüper Lig</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>23/08 18:30</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2,10%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+26,2%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45892.35123584756</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 27.5 - tirs | Atlético M</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Atlético Madrid – ElcheEspagne - Espagne LaLiga</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Plus que 27.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>23/08 17:30</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>40,2%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+24,5%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45892.35123584756</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Moins que 22.5 - tirs | Brentford </t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Brentford – Aston VillaPremier League</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Moins que 22.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>23/08 14:00</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>38,1%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+12,2%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45892.35123584756</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-23.xlsx
+++ b/data/valuebets_database_2025-08-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1967,10 +1967,8 @@
           <t>23/08 18:30</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F36" t="n">
+        <v>60</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1983,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45892.35123584756</v>
+        <v>45892.35123584491</v>
       </c>
     </row>
     <row r="37">
@@ -2012,10 +2010,8 @@
           <t>23/08 17:30</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="F37" t="n">
+        <v>3.1</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2028,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45892.35123584756</v>
+        <v>45892.35123584491</v>
       </c>
     </row>
     <row r="38">
@@ -2057,10 +2053,8 @@
           <t>23/08 14:00</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2.95</t>
-        </is>
+      <c r="F38" t="n">
+        <v>2.95</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2073,7 +2067,142 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45892.35123584756</v>
+        <v>45892.35123584491</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | H 1 (−2.5) | Federico A</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Federico Agustin Gomez – Jack DraperUS Open (H)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>H 1 (−2.5)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>25/08 16:10</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+192%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45892.38904296764</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | H 2 (−2.5) | Ben Shelto</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ben Shelton – Ignacio BuseUS Open (H)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>H 2 (−2.5)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>24/08 16:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+77,9%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45892.38904296764</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 2 | Rapid Buca</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Rapid Bucarest – UTA AradRoumanie. Roumanie - Liga I - YYUZJR 385076e7</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>30/08 15:00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>27,8%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+16,7%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45892.38904296764</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-23.xlsx
+++ b/data/valuebets_database_2025-08-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2096,10 +2096,8 @@
           <t>25/08 16:10</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>150</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2112,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45892.38904296764</v>
+        <v>45892.38904296296</v>
       </c>
     </row>
     <row r="40">
@@ -2141,10 +2139,8 @@
           <t>24/08 16:00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F40" t="n">
+        <v>100</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2157,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45892.38904296764</v>
+        <v>45892.38904296296</v>
       </c>
     </row>
     <row r="41">
@@ -2186,10 +2182,8 @@
           <t>30/08 15:00</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
+      <c r="F41" t="n">
+        <v>4.2</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2202,7 +2196,142 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45892.38904296764</v>
+        <v>45892.38904296296</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 28.5 - tirs | Columbus C</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Columbus Crew – New England RevolutionÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Plus que 28.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>23/08 23:30</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>49,5%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+48,5%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45892.43130172107</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 11.5 - tirs1re équipe | FC St. Pau</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>FC St. Pauli – DortmundBundesliga</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Plus que 11.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>23/08 16:30</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>44,5%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+17,8%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45892.43130172107</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | FC Botosan</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>FC Botosani – FK Csikszereda Miercurea CiucLiga 1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>23/08 15:45</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+13,6%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45892.43130172107</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-23.xlsx
+++ b/data/valuebets_database_2025-08-23.xlsx
@@ -2225,10 +2225,8 @@
           <t>23/08 23:30</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>3</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2241,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45892.43130172107</v>
+        <v>45892.43130172454</v>
       </c>
     </row>
     <row r="43">
@@ -2270,10 +2268,8 @@
           <t>23/08 16:30</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
+      <c r="F43" t="n">
+        <v>2.65</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2286,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45892.43130172107</v>
+        <v>45892.43130172454</v>
       </c>
     </row>
     <row r="44">
@@ -2315,10 +2311,8 @@
           <t>23/08 15:45</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>50</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2331,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45892.43130172107</v>
+        <v>45892.43130172454</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-23.xlsx
+++ b/data/valuebets_database_2025-08-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2328,6 +2328,186 @@
         <v>45892.43130172454</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Lulea HF –</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Lulea HF – EV ZugLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>28/08 17:00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+162%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45892.5278963991</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | UNA Strass</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>UNA Strassen – UT PétangeNational Division</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>24/08 14:00</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+17,7%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45892.5278963991</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Moins que 24.5 - tirs | Levante – </t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Levante – BarceloneEspagne - Espagne LaLiga</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Moins que 24.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>23/08 19:30</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>37,6%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+12,8%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45892.5278963991</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Gremio – C</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Gremio – Ceara SCSérie A</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>24/08 00:00</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+11,8%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45892.5278963991</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-23.xlsx
+++ b/data/valuebets_database_2025-08-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2354,10 +2354,8 @@
           <t>28/08 17:00</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>150</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2370,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45892.5278963991</v>
+        <v>45892.52789640046</v>
       </c>
     </row>
     <row r="46">
@@ -2399,10 +2397,8 @@
           <t>24/08 14:00</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F46" t="n">
+        <v>40</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2415,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45892.5278963991</v>
+        <v>45892.52789640046</v>
       </c>
     </row>
     <row r="47">
@@ -2444,10 +2440,8 @@
           <t>23/08 19:30</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F47" t="n">
+        <v>3</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2460,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45892.5278963991</v>
+        <v>45892.52789640046</v>
       </c>
     </row>
     <row r="48">
@@ -2489,10 +2483,8 @@
           <t>24/08 00:00</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>50</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2505,7 +2497,97 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45892.5278963991</v>
+        <v>45892.52789640046</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>PMU(FR)Tennis | Moins que 8.51er set | Kym, Jérôm</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>PMU(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Kym, Jérôme – Quinn, EthanEvénements. US Open (H)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Moins que 8.51er set</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>24/08 19:00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>19,3%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+35,3%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45892.56022719455</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 21.5 - tirs | Sassuolo –</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Sassuolo – NaplesItalie - Italie Serie A</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Moins que 21.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>23/08 16:30</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>33,4%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+13,5%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45892.56022719455</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-23.xlsx
+++ b/data/valuebets_database_2025-08-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2526,10 +2526,8 @@
           <t>24/08 19:00</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
+      <c r="F49" t="n">
+        <v>7</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2542,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45892.56022719455</v>
+        <v>45892.56022719907</v>
       </c>
     </row>
     <row r="50">
@@ -2571,10 +2569,8 @@
           <t>23/08 16:30</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="F50" t="n">
+        <v>3.4</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2587,7 +2583,502 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45892.56022719455</v>
+        <v>45892.56022719907</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Frölunda H</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Frölunda HC – BolzanoEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>29/08 17:00</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>250.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+323%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45892.59610352702</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Mountfield</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Mountfield HK – Odense BulldogsEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>29/08 15:30</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>225.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+297%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45892.59610352702</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Salzbourg </t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Salzbourg – TychyEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>29/08 18:20</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>225.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+288%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45892.59610352702</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Belfast Gi</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Belfast Giants – KalPaLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>28/08 18:00</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+257%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45892.59610352702</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Ingolstadt</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ingolstadt – Ilves TampereEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>28/08 17:30</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+230%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45892.59610352702</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | KAC Klagen</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>KAC Klagenfurt – Sparta PragueLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>28/08 18:20</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1,80%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+215%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45892.59610352702</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Luleå HF –</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Luleå HF – ZugEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>28/08 17:00</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+210%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45892.59610352702</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Storhamar </t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Storhamar – BerlinLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>28/08 17:00</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+176%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45892.59610352702</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Lukko – La</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Lukko – LausanneEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>29/08 15:30</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+169%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45892.59610352702</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | HC Kometa </t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>HC Kometa Brno – Brynas IFLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>29/08 17:00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+157%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45892.59610352702</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | ZSC Lions </t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ZSC Lions – Pinguins BremerhavenLigue des Champions - YYUZJR 385076e7</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>29/08 17:45</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+129%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45892.59610352702</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-23.xlsx
+++ b/data/valuebets_database_2025-08-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2612,10 +2612,8 @@
           <t>29/08 17:00</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>250.00</t>
-        </is>
+      <c r="F51" t="n">
+        <v>250</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2628,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45892.59610352702</v>
+        <v>45892.59610353009</v>
       </c>
     </row>
     <row r="52">
@@ -2657,10 +2655,8 @@
           <t>29/08 15:30</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
+      <c r="F52" t="n">
+        <v>225</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2673,7 +2669,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45892.59610352702</v>
+        <v>45892.59610353009</v>
       </c>
     </row>
     <row r="53">
@@ -2702,10 +2698,8 @@
           <t>29/08 18:20</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
+      <c r="F53" t="n">
+        <v>225</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2718,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45892.59610352702</v>
+        <v>45892.59610353009</v>
       </c>
     </row>
     <row r="54">
@@ -2747,10 +2741,8 @@
           <t>28/08 18:00</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>200</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2763,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45892.59610352702</v>
+        <v>45892.59610353009</v>
       </c>
     </row>
     <row r="55">
@@ -2792,10 +2784,8 @@
           <t>28/08 17:30</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F55" t="n">
+        <v>175</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2808,7 +2798,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45892.59610352702</v>
+        <v>45892.59610353009</v>
       </c>
     </row>
     <row r="56">
@@ -2837,10 +2827,8 @@
           <t>28/08 18:20</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F56" t="n">
+        <v>175</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2853,7 +2841,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45892.59610352702</v>
+        <v>45892.59610353009</v>
       </c>
     </row>
     <row r="57">
@@ -2882,10 +2870,8 @@
           <t>28/08 17:00</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>175</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2898,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45892.59610352702</v>
+        <v>45892.59610353009</v>
       </c>
     </row>
     <row r="58">
@@ -2927,10 +2913,8 @@
           <t>28/08 17:00</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F58" t="n">
+        <v>150</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2943,7 +2927,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45892.59610352702</v>
+        <v>45892.59610353009</v>
       </c>
     </row>
     <row r="59">
@@ -2972,10 +2956,8 @@
           <t>29/08 15:30</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F59" t="n">
+        <v>150</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2988,7 +2970,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45892.59610352702</v>
+        <v>45892.59610353009</v>
       </c>
     </row>
     <row r="60">
@@ -3017,10 +2999,8 @@
           <t>29/08 17:00</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F60" t="n">
+        <v>140</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3033,7 +3013,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45892.59610352702</v>
+        <v>45892.59610353009</v>
       </c>
     </row>
     <row r="61">
@@ -3062,10 +3042,8 @@
           <t>29/08 17:45</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F61" t="n">
+        <v>125</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3078,7 +3056,52 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45892.59610352702</v>
+        <v>45892.59610353009</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Belfast Gi</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Belfast Giants – KalPaEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>28/08 18:00</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+257%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45892.63852092649</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-23.xlsx
+++ b/data/valuebets_database_2025-08-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3085,23 +3085,156 @@
           <t>28/08 18:00</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F62" t="n">
+        <v>200</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+257%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45892.63852092592</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Mountfield</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Mountfield HK – Odense BulldogsLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>29/08 15:30</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>200.00</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>+257%</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="n">
-        <v>45892.63852092649</v>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+239%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45892.6830133939</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | ERC Ingols</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ERC Ingolstadt – Ilves TampereLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>28/08 17:30</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+220%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45892.6830133939</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Kometa Brn</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Kometa Brno – Brynäs IFEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>29/08 17:00</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+155%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45892.6830133939</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-23.xlsx
+++ b/data/valuebets_database_2025-08-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3128,10 +3128,8 @@
           <t>29/08 15:30</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F63" t="n">
+        <v>200</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3144,7 +3142,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45892.6830133939</v>
+        <v>45892.6830133912</v>
       </c>
     </row>
     <row r="64">
@@ -3173,10 +3171,8 @@
           <t>28/08 17:30</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F64" t="n">
+        <v>175</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3189,7 +3185,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45892.6830133939</v>
+        <v>45892.6830133912</v>
       </c>
     </row>
     <row r="65">
@@ -3218,10 +3214,8 @@
           <t>29/08 17:00</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F65" t="n">
+        <v>140</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3234,7 +3228,97 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45892.6830133939</v>
+        <v>45892.6830133912</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | KAC – Spar</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>KAC – Sparta PragueEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>28/08 18:20</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+211%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45892.72004549117</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Maccabi Ha</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Maccabi Haifa – Maccabi Bnei Reina385076e7 Premier League</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>23/08 17:30</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+23,2%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45892.72004549117</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-23.xlsx
+++ b/data/valuebets_database_2025-08-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3257,10 +3257,8 @@
           <t>28/08 18:20</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F66" t="n">
+        <v>175</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3273,7 +3271,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45892.72004549117</v>
+        <v>45892.72004548611</v>
       </c>
     </row>
     <row r="67">
@@ -3302,10 +3300,8 @@
           <t>23/08 17:30</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F67" t="n">
+        <v>50</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3318,7 +3314,52 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45892.72004549117</v>
+        <v>45892.72004548611</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Storhamar </t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Storhamar IL Dragons – Eisbären BerlinEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>28/08 17:00</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+168%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45892.76925117424</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-23.xlsx
+++ b/data/valuebets_database_2025-08-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3343,10 +3343,8 @@
           <t>28/08 17:00</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F68" t="n">
+        <v>150</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3359,7 +3357,52 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45892.76925117424</v>
+        <v>45892.76925116898</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | RB Salzbou</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>RB Salzbourg – Gorniczy Klub Sportowy TychyLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>29/08 18:20</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>+248%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>45892.80284756486</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-23.xlsx
+++ b/data/valuebets_database_2025-08-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3386,10 +3386,8 @@
           <t>29/08 18:20</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F69" t="n">
+        <v>200</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3402,7 +3400,52 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45892.80284756486</v>
+        <v>45892.80284756944</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Lukko Raum</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Lukko Rauma – Lausanne385076e7 Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>29/08 15:30</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>+155%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>45892.84841798482</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-23.xlsx
+++ b/data/valuebets_database_2025-08-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3429,10 +3429,8 @@
           <t>29/08 15:30</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F70" t="n">
+        <v>140</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3445,7 +3443,52 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>45892.84841798482</v>
+        <v>45892.84841798611</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 1 - aces | L.Sonego –</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>L.Sonego – T.SchoolkateATP - US Open H</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>25/08 15:00</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>53,1%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>+46,0%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>45892.88780237819</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-23.xlsx
+++ b/data/valuebets_database_2025-08-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3472,23 +3472,111 @@
           <t>25/08 15:00</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F71" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>53,1%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>+46,0%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>45892.88780237269</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | La Equidad</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>La Equidad – AD PastoPrimera A</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>30/08 21:10</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2,69%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>+34,7%</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>45892.93002767558</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 1 - aces | V.Royer – </t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>V.Royer – Y.BuATP - US Open H</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>25/08 15:00</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>2.75</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>53,1%</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>+46,0%</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="n">
-        <v>45892.88780237819</v>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>46,7%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>+28,3%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>45892.93002767558</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-23.xlsx
+++ b/data/valuebets_database_2025-08-23.xlsx
@@ -3515,10 +3515,8 @@
           <t>30/08 21:10</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F72" t="n">
+        <v>50</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3531,7 +3529,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>45892.93002767558</v>
+        <v>45892.93002767361</v>
       </c>
     </row>
     <row r="73">
@@ -3560,10 +3558,8 @@
           <t>25/08 15:00</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F73" t="n">
+        <v>2.75</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3576,7 +3572,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>45892.93002767558</v>
+        <v>45892.93002767361</v>
       </c>
     </row>
   </sheetData>
